--- a/testdata/testdata.xlsx
+++ b/testdata/testdata.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8791a13343266f08/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8791a13343266f08/Desktop/AppolloAutomation/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D824BDC-80F4-4532-AE58-61A38B472BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{8D824BDC-80F4-4532-AE58-61A38B472BE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53B610BB-1F1E-4ECF-B8B9-813E927EEF6D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{45159AF6-DEB7-4EF4-BBE8-CEF90E5A3859}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>package_name</t>
   </si>
@@ -49,6 +49,33 @@
   </si>
   <si>
     <t>Thyroid</t>
+  </si>
+  <si>
+    <t>mobile_number</t>
+  </si>
+  <si>
+    <t>card_name</t>
+  </si>
+  <si>
+    <t>card_number</t>
+  </si>
+  <si>
+    <t>expiry_date</t>
+  </si>
+  <si>
+    <t>cvv</t>
+  </si>
+  <si>
+    <t>Teja Sai</t>
+  </si>
+  <si>
+    <t>Rahul</t>
+  </si>
+  <si>
+    <t>Ram</t>
+  </si>
+  <si>
+    <t>Manikanta</t>
   </si>
 </sst>
 </file>
@@ -434,32 +461,111 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CB91EF2-EC1A-406C-BE3C-7A7F19EEC738}">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.21875" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2">
+        <v>9381866215</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2">
+        <v>4111111111111110</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1230</v>
+      </c>
+      <c r="F2" s="2">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="B3" s="2">
+        <v>9381866215</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="2">
+        <v>5555555555554440</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1128</v>
+      </c>
+      <c r="F3" s="2">
+        <v>456</v>
+      </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
+      <c r="B4">
+        <v>938186625</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
+        <v>459612357894</v>
+      </c>
+      <c r="E4">
+        <v>1129</v>
+      </c>
+      <c r="F4">
+        <v>541</v>
+      </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
+      <c r="B5">
+        <v>9381866215</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5">
+        <v>856942567841</v>
+      </c>
+      <c r="E5">
+        <v>1033</v>
+      </c>
+      <c r="F5">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
